--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/GEORGIA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/GEORGIA_2022.xlsx
@@ -1849,7 +1849,7 @@
         <v>13</v>
       </c>
       <c r="D83">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="84">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C164">
@@ -3775,7 +3775,7 @@
         <v>13</v>
       </c>
       <c r="D190">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="191">
@@ -4729,7 +4729,7 @@
         <v>13</v>
       </c>
       <c r="D243">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="244">
@@ -4801,7 +4801,7 @@
         <v>13</v>
       </c>
       <c r="D247">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="248">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C275">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C285">
@@ -6493,7 +6493,7 @@
         <v>13</v>
       </c>
       <c r="D341">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="342">
@@ -6547,7 +6547,7 @@
         <v>13</v>
       </c>
       <c r="D344">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="345">
@@ -6997,7 +6997,7 @@
         <v>13</v>
       </c>
       <c r="D369">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="370">
@@ -7285,7 +7285,7 @@
         <v>13</v>
       </c>
       <c r="D385">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="386">
@@ -7879,7 +7879,7 @@
         <v>13</v>
       </c>
       <c r="D418">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="419">
@@ -8149,7 +8149,7 @@
         <v>13</v>
       </c>
       <c r="D433">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="434">
@@ -8905,7 +8905,7 @@
         <v>135</v>
       </c>
       <c r="D475">
-        <v>0.009538613721472479</v>
+        <v>0.00953861372147248</v>
       </c>
     </row>
     <row r="476">
@@ -12091,7 +12091,7 @@
         <v>13</v>
       </c>
       <c r="D652">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="653">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C687">
@@ -13009,7 +13009,7 @@
         <v>13</v>
       </c>
       <c r="D703">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="704">
@@ -13279,7 +13279,7 @@
         <v>13</v>
       </c>
       <c r="D718">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="719">
@@ -13621,7 +13621,7 @@
         <v>13</v>
       </c>
       <c r="D737">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="738">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C779">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C821">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C828">
@@ -18787,7 +18787,7 @@
         <v>13</v>
       </c>
       <c r="D1024">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="1025">
@@ -19165,7 +19165,7 @@
         <v>13</v>
       </c>
       <c r="D1045">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="1046">
@@ -20371,7 +20371,7 @@
         <v>13</v>
       </c>
       <c r="D1112">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="1113">
@@ -21073,7 +21073,7 @@
         <v>13</v>
       </c>
       <c r="D1151">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="1152">
@@ -22207,7 +22207,7 @@
         <v>13</v>
       </c>
       <c r="D1214">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="1215">
@@ -23575,7 +23575,7 @@
         <v>13</v>
       </c>
       <c r="D1290">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="1291">
@@ -24313,7 +24313,7 @@
         <v>13</v>
       </c>
       <c r="D1331">
-        <v>0.0009185331731788313</v>
+        <v>0.0009185331731788312</v>
       </c>
     </row>
     <row r="1332">
